--- a/docs/oc-regiones/suministro-de-combustibles/coquimbo.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M373"/>
+  <dimension ref="A1:M377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4274.89</v>
+        <v>4238.68</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2222.94</v>
+        <v>2211.52</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9404.75</v>
+        <v>9356.43</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3206.16</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6932.23</v>
+        <v>6896.61</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13893.38</v>
+        <v>13754.72</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.4</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.44</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.05</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2244.32</v>
+        <v>2219.31</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4999.48</v>
+        <v>4972.1</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.42</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3740.53</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2346.06</v>
+        <v>2343.07</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4799.75</v>
+        <v>4851.95</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2229.63</v>
+        <v>2253.88</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6952.5</v>
+        <v>7028.11</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4809.25</v>
+        <v>4861.55</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14962.1</v>
+        <v>15220.37</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4274.89</v>
+        <v>4348.68</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5343.61</v>
+        <v>5380.63</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6412.33</v>
+        <v>6442.19</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5343.61</v>
+        <v>5368.49</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2284.93</v>
+        <v>2301.4</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8015.41</v>
+        <v>8073.2</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>44886.3</v>
+        <v>44806.69</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6412.33</v>
+        <v>6385.9</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5594.76</v>
+        <v>5571.7</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3143.11</v>
+        <v>3130.16</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>14000.25</v>
+        <v>13978.55</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7694.79</v>
+        <v>7682.87</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12824.66</v>
+        <v>12915.17</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12824.66</v>
+        <v>12915.17</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>15496.46</v>
+        <v>15605.83</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2426.29</v>
+        <v>2443.41</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.2</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3274.53</v>
+        <v>3232.93</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7080.04</v>
+        <v>6990.11</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3885.62</v>
+        <v>3846.96</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3274.53</v>
+        <v>3241.95</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>5457.54</v>
+        <v>5403.24</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10915.09</v>
+        <v>10806.49</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6549.05</v>
+        <v>6525.57</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5199.4</v>
+        <v>5180.76</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2455.89</v>
+        <v>2450.58</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3274.53</v>
+        <v>3267.44</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5457.54</v>
+        <v>5445.73</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5708.59</v>
+        <v>5642.53</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4911.79</v>
+        <v>4854.95</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.89</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3820.28</v>
+        <v>3834.94</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>25104.7</v>
+        <v>25201.06</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2401.32</v>
+        <v>2410.54</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>10915.09</v>
+        <v>10964.55</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2281.25</v>
+        <v>2291.59</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4366.04</v>
+        <v>4377.61</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4242.69</v>
+        <v>4253.95</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4366.04</v>
+        <v>4359.91</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2292.17</v>
+        <v>2288.95</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2947.07</v>
+        <v>2942.94</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>16263.48</v>
+        <v>16240.67</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2281.25</v>
+        <v>2284.18</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>20738.67</v>
+        <v>20765.25</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3274.53</v>
+        <v>3278.72</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2292.17</v>
+        <v>2307.95</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4366.04</v>
+        <v>4396.09</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>33760.37</v>
+        <v>33992.75</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3274.53</v>
+        <v>3302.51</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2292.17</v>
+        <v>2311.76</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>6549.05</v>
+        <v>6605.02</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6549.05</v>
+        <v>6619.3</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>74222.60000000001</v>
+        <v>75134.8</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>13643.86</v>
+        <v>13811.54</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4693.49</v>
+        <v>4753.8</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>41613.48</v>
+        <v>41841.06</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3274.53</v>
+        <v>3292.43</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4038.58</v>
+        <v>4060.67</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15062.82</v>
+        <v>15145.2</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>63174.57</v>
+        <v>63520.06</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5656.33</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>12841</v>
+        <v>12513.09</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5792.08</v>
+        <v>5644.17</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3959.43</v>
+        <v>3858.32</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>22625.31</v>
+        <v>22184.02</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7337.92</v>
+        <v>7166.26</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2454.51</v>
+        <v>2397.09</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8031.99</v>
+        <v>7916.86</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4525.06</v>
+        <v>4467.63</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>38462.99</v>
+        <v>37965.88</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>5656.33</v>
+        <v>5645.19</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3959.43</v>
+        <v>3959.46</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5215.7</v>
+        <v>5222.94</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>16968.98</v>
+        <v>16910.75</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>18665.88</v>
+        <v>18601.82</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>15837.72</v>
+        <v>15783.36</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>33937.97</v>
+        <v>33821.49</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6108.83</v>
+        <v>6087.87</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>5718.55</v>
+        <v>5698.92</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4242.25</v>
+        <v>4227.69</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>15837.72</v>
+        <v>15783.36</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>6787.59</v>
+        <v>6751.74</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3959.43</v>
+        <v>3985.38</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3393.8</v>
+        <v>3445.46</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>18665.88</v>
+        <v>18950.05</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7692.61</v>
+        <v>7887.08</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>9615.76</v>
+        <v>9858.84</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4525.06</v>
+        <v>4662.28</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>18100.25</v>
+        <v>18649.11</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>34801.98</v>
+        <v>34981.75</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>8004.45</v>
+        <v>7970.7</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>74244.22</v>
+        <v>73931.17</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2465.84</v>
+        <v>2472.61</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>6960.4</v>
+        <v>7023.71</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>19373.1</v>
+        <v>19549.31</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>5759.15</v>
+        <v>5811.53</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5238.86</v>
+        <v>5275.33</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>16240.92</v>
+        <v>16347.88</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2668.15</v>
+        <v>2665.4</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>12644.72</v>
+        <v>12554.13</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>26919.33</v>
+        <v>26726.48</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2900.16</v>
+        <v>2879.39</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>6960.4</v>
+        <v>6922.49</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4988.28</v>
+        <v>4958.89</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>69603.95</v>
+        <v>69193.78</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>7888.45</v>
+        <v>7840.51</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4060.23</v>
+        <v>4044.56</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5678.52</v>
+        <v>5707.92</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5800.33</v>
+        <v>5830.36</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4060.23</v>
+        <v>4064.14</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5176.21</v>
+        <v>5181.2</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>40091.85</v>
+        <v>40130.49</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2527.77</v>
+        <v>2639.4</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>30783.27</v>
+        <v>32142.72</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7693.21</v>
+        <v>8032.96</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>14836.91</v>
+        <v>15267.87</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4945.64</v>
+        <v>4965.13</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>16485.45</v>
+        <v>16550.45</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3876.88</v>
+        <v>3886.42</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>15386.42</v>
+        <v>15188.34</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2312.08</v>
+        <v>2295.77</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3846.61</v>
+        <v>3916.35</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6594.18</v>
+        <v>6697.48</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>32970.9</v>
+        <v>32969.21</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5495.15</v>
+        <v>5494.87</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2417.87</v>
+        <v>2417.74</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>4396.12</v>
+        <v>4376.46</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>30992.65</v>
+        <v>31019.35</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>7143.7</v>
+        <v>7149.85</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2359.18</v>
+        <v>2361.21</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5495.15</v>
+        <v>5479.99</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>10990.3</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>10990.3</v>
+        <v>10863.43</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5495.15</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5385.25</v>
+        <v>5304.92</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>14287.39</v>
+        <v>14074.29</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5486.49</v>
+        <v>5454.97</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6813.99</v>
+        <v>6774.85</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>32970.9</v>
+        <v>32759.68</v>
       </c>
     </row>
     <row r="188">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2288-293-CM26</t>
+          <t>2146-124-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8792.24</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="190">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6594.18</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2146-124-CM26</t>
+          <t>2288-293-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4396.12</v>
+        <v>8735.91</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5495.15</v>
+        <v>5471.48</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>21980.6</v>
+        <v>21662.6</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7891.04</v>
+        <v>7721.26</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4121.36</v>
+        <v>4032.69</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>7693.21</v>
+        <v>7514.2</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>8698.82</v>
+        <v>8496.41</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>584335.37</v>
+        <v>572811.47</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>4454.91</v>
+        <v>4374.12</v>
       </c>
     </row>
     <row r="201">
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>15592.18</v>
+        <v>15309.41</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3597-227-CM26</t>
+          <t>1242121-164-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12738,17 +12738,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12773,13 +12773,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>22274.54</v>
+        <v>5419.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1242121-164-CM26</t>
+          <t>3597-227-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12799,17 +12799,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5568.63</v>
+        <v>21678.1</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>20938.07</v>
+        <v>20999.02</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2338.83</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7239.22</v>
+        <v>7269.31</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.24</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5414.12</v>
+        <v>5436.63</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>13364.72</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>53158.18</v>
+        <v>53609.34</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>6682.36</v>
+        <v>6739.07</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5011.77</v>
+        <v>5003.39</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4454.91</v>
+        <v>4447.46</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3898.04</v>
+        <v>3946.02</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3341.18</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>4454.91</v>
+        <v>4509.74</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>16705.9</v>
+        <v>16911.51</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3898.04</v>
+        <v>3949.94</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>8820.719999999999</v>
+        <v>9037.790000000001</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2450.2</v>
+        <v>2510.5</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3898.04</v>
+        <v>3993.97</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>10023.54</v>
+        <v>10213.11</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>7796.09</v>
+        <v>7884.75</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>37866.71</v>
+        <v>38207.83</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>16149.04</v>
+        <v>16294.51</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7796.09</v>
+        <v>7866.32</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>5568.63</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>33413.34</v>
+        <v>33627.04</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>5568.63</v>
+        <v>5604.25</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2784.32</v>
+        <v>2802.13</v>
       </c>
     </row>
     <row r="232">
@@ -14603,13 +14603,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>18933.36</v>
+        <v>18992.93</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4433-24-CM26</t>
+          <t>3884-213-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14664,13 +14664,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3653.02</v>
+        <v>8205.84</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3884-213-CM26</t>
+          <t>4433-24-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>8171.97</v>
+        <v>3668.17</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2444.68</v>
+        <v>2454.81</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>17262.77</v>
+        <v>17334.32</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3898.04</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>10580.41</v>
+        <v>10624.26</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3341.18</v>
+        <v>3326.83</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9010.049999999999</v>
+        <v>8971.34</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3899.12</v>
+        <v>3875.75</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2450.88</v>
+        <v>2417.56</v>
       </c>
     </row>
     <row r="243">
@@ -15274,13 +15274,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4456.14</v>
+        <v>4395.56</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057439-3035-CM26</t>
+          <t>1242121-232-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4790.35</v>
+        <v>6627.2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1242121-232-CM26</t>
+          <t>1057439-3035-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15396,13 +15396,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>6684.21</v>
+        <v>4749.49</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2711-111-CM26</t>
+          <t>1159-90-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15457,13 +15457,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5013.16</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1432-14-CM26</t>
+          <t>1159-91-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15483,17 +15483,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15503,12 +15503,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>5570.17</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1159-90-CM26</t>
+          <t>1343-95-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15544,17 +15544,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.042-8</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15579,13 +15579,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>22280.7</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1159-91-CM26</t>
+          <t>1432-14-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15605,17 +15605,17 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15625,12 +15625,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15640,13 +15640,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>22280.7</v>
+        <v>5600.17</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1343-95-CM26</t>
+          <t>2711-111-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15666,17 +15666,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>60.511.042-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2359.53</v>
+        <v>5040.15</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>18938.59</v>
+        <v>19150.4</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>22280.7</v>
+        <v>22529.88</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>10583.33</v>
+        <v>10701.69</v>
       </c>
     </row>
     <row r="254">
@@ -15945,13 +15945,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2359.12</v>
+        <v>2376.99</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3512-482-CM26</t>
+          <t>2553-5-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15971,17 +15971,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16006,13 +16006,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6582.98</v>
+        <v>4602.14</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2553-5-CM26</t>
+          <t>3512-482-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16032,17 +16032,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>4567.54</v>
+        <v>6632.84</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.66</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>4456.14</v>
+        <v>4489.89</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>20609.65</v>
+        <v>20765.75</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>4344.74</v>
+        <v>4361.2</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>8761.879999999999</v>
+        <v>8795.08</v>
       </c>
     </row>
     <row r="262">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>7798.24</v>
+        <v>7778.56</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1229788-107-CM26</t>
+          <t>3512-490-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16494,13 +16494,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>47123.68</v>
+        <v>16306.98</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1660-366-CM26</t>
+          <t>1229788-107-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>12365.79</v>
+        <v>47571.39</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2288-429-CM26</t>
+          <t>1660-366-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16601,12 +16601,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16616,13 +16616,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>16710.52</v>
+        <v>12483.27</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2125-1059-CM26</t>
+          <t>2288-429-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16647,12 +16647,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16662,12 +16662,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16677,13 +16677,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6684.21</v>
+        <v>16869.29</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3512-490-CM26</t>
+          <t>2125-1059-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>16153.51</v>
+        <v>6747.71</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>16710.52</v>
+        <v>16835.02</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3342.1</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3049.11</v>
+        <v>3071.83</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>27442.02</v>
+        <v>27646.46</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3899.12</v>
+        <v>3928.17</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4456.14</v>
+        <v>4411.7</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>24954.38</v>
+        <v>24705.52</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>33421.05</v>
+        <v>33057.49</v>
       </c>
     </row>
     <row r="277">
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>4456.14</v>
+        <v>4446.03</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1346282-232-CM26</t>
+          <t>5158-58-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17374,17 +17374,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4790.35</v>
+        <v>8956.059999999999</v>
       </c>
     </row>
     <row r="279">
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5013.16</v>
+        <v>5037.78</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5158-58-CM26</t>
+          <t>1346282-232-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17496,17 +17496,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>4813.88</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>7241.23</v>
+        <v>7276.8</v>
       </c>
     </row>
     <row r="282">
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>31409.97</v>
+        <v>31564.26</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>624-79-CM26</t>
+          <t>1432-19-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17684,12 +17684,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17714,13 +17714,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>11140.35</v>
+        <v>2794.33</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2992-173-CM26</t>
+          <t>624-79-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17745,12 +17745,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17775,13 +17775,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>33421.05</v>
+        <v>11177.31</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1432-19-CM26</t>
+          <t>2992-173-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17806,12 +17806,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17821,12 +17821,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2785.09</v>
+        <v>33531.92</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3397.58</v>
+        <v>3408.4</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>33421.05</v>
+        <v>33598.76</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8394.25</v>
+        <v>8438.889999999999</v>
       </c>
     </row>
     <row r="289">
@@ -18080,13 +18080,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2435.29</v>
+        <v>2470.13</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3512-541-CM26</t>
+          <t>1242121-283-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18106,17 +18106,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>17711.18</v>
+        <v>6719.6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3707-286-CM26</t>
+          <t>4433-33-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18167,17 +18167,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>7748.64</v>
+        <v>3502.63</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3616-69-CM26</t>
+          <t>3750-150-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18233,12 +18233,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18263,13 +18263,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4427.79</v>
+        <v>4479.73</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3750-150-CM26</t>
+          <t>3616-69-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18324,13 +18324,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4427.79</v>
+        <v>4479.73</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4433-33-CM26</t>
+          <t>3707-286-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18350,17 +18350,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18385,13 +18385,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3462.02</v>
+        <v>7839.54</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1242121-283-CM26</t>
+          <t>3512-541-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18411,17 +18411,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18446,13 +18446,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>6641.69</v>
+        <v>17918.94</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2450-617-CM26</t>
+          <t>2125-1225-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18507,13 +18507,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>37629.69</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4247-335-CM26</t>
+          <t>3265-271-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18538,12 +18538,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18553,12 +18553,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18568,13 +18568,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>11069.49</v>
+        <v>14915.12</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3265-270-CM26</t>
+          <t>4247-335-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18599,12 +18599,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18614,12 +18614,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>23113.09</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3265-271-CM26</t>
+          <t>2450-617-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18655,17 +18655,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18690,13 +18690,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>14667.07</v>
+        <v>38266.1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2125-1225-CM26</t>
+          <t>3265-270-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18716,17 +18716,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>6641.69</v>
+        <v>23503.98</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5313.35</v>
+        <v>5367.39</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>7599.2</v>
+        <v>7676.48</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2767.37</v>
+        <v>2793.33</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>22692.45</v>
+        <v>22520.3</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2374.6</v>
+        <v>2334.48</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>16604.23</v>
+        <v>16368.58</v>
       </c>
     </row>
     <row r="307">
@@ -19178,13 +19178,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>36529.3</v>
+        <v>36010.87</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4773-11-CM26</t>
+          <t>1962-333-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19209,12 +19209,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19224,12 +19224,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2391.01</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>697055-31-CM26</t>
+          <t>4036-278-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19265,17 +19265,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19300,13 +19300,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>5534.74</v>
+        <v>24673.3</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1057440-323-CM26</t>
+          <t>4773-11-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19331,12 +19331,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19346,12 +19346,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19361,13 +19361,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3874.32</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4036-278-CM26</t>
+          <t>697055-31-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19387,17 +19387,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19422,13 +19422,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>25017.04</v>
+        <v>5458.69</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1962-333-CM26</t>
+          <t>1057440-323-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19453,12 +19453,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2767.37</v>
+        <v>3821.09</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3874.32</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>5534.74</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="315">
@@ -19666,13 +19666,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>5584.67</v>
+        <v>5550.04</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3707-319-CM26</t>
+          <t>3688-281-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19692,17 +19692,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19727,13 +19727,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>8374.07</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1962-343-CM26</t>
+          <t>3687-169-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19753,17 +19753,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19788,13 +19788,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>3932.01</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>3688-281-CM26</t>
+          <t>1962-343-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19814,17 +19814,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19849,13 +19849,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>4427.79</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3687-169-CM26</t>
+          <t>3707-319-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19875,17 +19875,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3874.32</v>
+        <v>8498.76</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1057438-135-CM26</t>
+          <t>2554-10-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19941,12 +19941,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>4427.79</v>
+        <v>4545.81</v>
       </c>
     </row>
     <row r="321">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3320.85</v>
+        <v>3383.98</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2554-10-CM26</t>
+          <t>1057438-135-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20063,12 +20063,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>4461</v>
+        <v>4511.97</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2712.02</v>
+        <v>2720.41</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4427.79</v>
+        <v>4441.48</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>9741.15</v>
+        <v>9771.26</v>
       </c>
     </row>
     <row r="326">
@@ -20337,13 +20337,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>11069.49</v>
+        <v>11103.71</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3512-603-CM26</t>
+          <t>1242121-330-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20363,17 +20363,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>17711.18</v>
+        <v>6624.13</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1276532-15-CM26</t>
+          <t>4773-13-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20444,12 +20444,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -20459,13 +20459,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2379.94</v>
+        <v>3864.07</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1242121-330-CM26</t>
+          <t>1276532-15-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20490,12 +20490,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>Administración Central</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20520,13 +20520,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>6641.69</v>
+        <v>2373.64</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4773-13-CM26</t>
+          <t>3512-603-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20546,17 +20546,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20566,12 +20566,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -20581,13 +20581,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3874.32</v>
+        <v>17664.33</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>3714-163-CM26</t>
+          <t>3707-342-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20612,12 +20612,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20642,13 +20642,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3320.85</v>
+        <v>7645.43</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3707-342-CM26</t>
+          <t>3714-163-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20673,12 +20673,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>7748.64</v>
+        <v>3276.61</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>18818.13</v>
+        <v>18449.78</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4427.79</v>
+        <v>4341.13</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3874.32</v>
+        <v>3798.48</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>5534.74</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>13836.86</v>
+        <v>13552.49</v>
       </c>
     </row>
     <row r="338">
@@ -21069,13 +21069,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>13836.86</v>
+        <v>13552.49</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3509-274-CM26</t>
+          <t>3707-345-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -21095,17 +21095,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>19334.67</v>
+        <v>7532.22</v>
       </c>
     </row>
     <row r="340">
@@ -21191,13 +21191,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>38404.03</v>
+        <v>38553.94</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3707-345-CM26</t>
+          <t>3509-274-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21217,17 +21217,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21252,13 +21252,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>7502.93</v>
+        <v>19410.15</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2125-1369-CM26</t>
+          <t>2711-165-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -21278,17 +21278,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21313,13 +21313,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>8593.190000000001</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2711-165-CM26</t>
+          <t>2125-1369-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21339,17 +21339,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5370.74</v>
+        <v>8679.610000000001</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3759.52</v>
+        <v>3797.17</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>6813.32</v>
+        <v>6839.85</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>26853.71</v>
+        <v>26717.68</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>4296.59</v>
+        <v>4274.83</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>16917.84</v>
+        <v>16832.14</v>
       </c>
     </row>
     <row r="349">
@@ -21740,13 +21740,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6670.46</v>
+        <v>6684.68</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1242121-353-CM26</t>
+          <t>931-126-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21771,12 +21771,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>6444.89</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="351">
@@ -21862,13 +21862,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2790.13</v>
+        <v>2796.08</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>931-126-CM26</t>
+          <t>1242121-353-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21893,12 +21893,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21923,13 +21923,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2309.42</v>
+        <v>6458.63</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1159-191-CM26</t>
+          <t>1057439-4664-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21949,17 +21949,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>15789.98</v>
+        <v>4648.95</v>
       </c>
     </row>
     <row r="354">
@@ -22045,13 +22045,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>17186.38</v>
+        <v>17298.42</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1057439-4664-CM26</t>
+          <t>1159-191-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22071,17 +22071,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>4618.84</v>
+        <v>15892.92</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>6981.97</v>
+        <v>6997.98</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>40280.57</v>
+        <v>40372.94</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>16112.23</v>
+        <v>16149.18</v>
       </c>
     </row>
     <row r="359">
@@ -22350,13 +22350,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>3222.45</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>527481-76-CM26</t>
+          <t>1057438-181-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22381,12 +22381,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>10777.15</v>
+        <v>7569.37</v>
       </c>
     </row>
     <row r="361">
@@ -22472,13 +22472,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2685.37</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1057438-181-CM26</t>
+          <t>527481-76-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -22503,12 +22503,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -22533,13 +22533,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>7519.04</v>
+        <v>10849.28</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1159-197-CM26</t>
+          <t>1159-198-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -22579,12 +22579,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr"/>
@@ -22594,13 +22594,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>21482.97</v>
+        <v>21415.11</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1159-198-CM26</t>
+          <t>3597-469-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -22625,12 +22625,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22640,12 +22640,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -22655,13 +22655,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>21482.97</v>
+        <v>21950.49</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>3597-469-CM26</t>
+          <t>1159-197-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -22686,12 +22686,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>22020.04</v>
+        <v>21415.11</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>10741.48</v>
+        <v>10718.11</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5371.48</v>
+        <v>5360.71</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>10311.83</v>
+        <v>10291.15</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2685.37</v>
+        <v>2679.99</v>
       </c>
     </row>
     <row r="370">
@@ -23021,13 +23021,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2717.6</v>
+        <v>2673.74</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2555-123-CM26</t>
+          <t>3707-390-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23047,17 +23047,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23082,13 +23082,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>4404.01</v>
+        <v>6568.8</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>3707-390-CM26</t>
+          <t>2555-123-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23108,17 +23108,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>6675.83</v>
+        <v>4333.4</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,251 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4296.59</v>
+        <v>4246.6</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>1057440-426-CM26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>61.606.403-7</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>3769.85</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>1495203-17-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>24489.71</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>4247-476-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>69.040.900-3</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>92.011.000-2</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>10938.65</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>3707-440-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>69.040.200-9</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>7478.35</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/coquimbo.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M874"/>
+  <dimension ref="A1:M875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -33339,7 +33339,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2710-13-CM26</t>
+          <t>3707-27-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33364,12 +33364,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>33821.49</v>
+        <v>5698.92</v>
       </c>
     </row>
     <row r="508">
@@ -33534,7 +33534,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3707-27-CM26</t>
+          <t>2710-13-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33559,12 +33559,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33593,7 +33593,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>5698.92</v>
+        <v>33821.49</v>
       </c>
     </row>
     <row r="511">
@@ -34379,7 +34379,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1159-23-CM26</t>
+          <t>3616-10-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34404,12 +34404,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -34419,17 +34419,17 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -34438,13 +34438,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>73931.17</v>
+        <v>7970.7</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>3616-10-CM26</t>
+          <t>1159-23-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34484,17 +34484,17 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>7970.7</v>
+        <v>73931.17</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4433-9-CM26</t>
+          <t>1242121-76-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34529,17 +34529,17 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2472.61</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1242121-76-CM26</t>
+          <t>3707-65-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34599,12 +34599,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34639,7 +34639,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>3707-65-CM26</t>
+          <t>4433-9-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34659,17 +34659,17 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -34698,13 +34698,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>5816.25</v>
+        <v>2472.61</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>3707-69-CM26</t>
+          <t>3614-15-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34729,12 +34729,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34763,13 +34763,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>5811.53</v>
+        <v>7023.71</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>3614-15-CM26</t>
+          <t>4036-97-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34789,17 +34789,17 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -34828,13 +34828,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>7023.71</v>
+        <v>19549.31</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>4036-97-CM26</t>
+          <t>3707-69-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34854,17 +34854,17 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34893,7 +34893,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>19549.31</v>
+        <v>5811.53</v>
       </c>
     </row>
     <row r="531">
@@ -35224,7 +35224,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1395-61-CM26</t>
+          <t>1229788-40-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35283,7 +35283,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>26726.48</v>
+        <v>12554.13</v>
       </c>
     </row>
     <row r="537">
@@ -35354,7 +35354,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1229788-40-CM26</t>
+          <t>1395-61-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35413,7 +35413,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>12554.13</v>
+        <v>26726.48</v>
       </c>
     </row>
     <row r="539">
@@ -35939,7 +35939,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>3884-132-CM26</t>
+          <t>2450-187-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35964,12 +35964,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>5181.2</v>
+        <v>40130.49</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1057438-49-CM26</t>
+          <t>3884-132-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36029,12 +36029,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -36063,13 +36063,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4064.14</v>
+        <v>5181.2</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2450-187-CM26</t>
+          <t>1057438-49-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -36094,12 +36094,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -36128,13 +36128,13 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>40130.49</v>
+        <v>4064.14</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2146-77-CM26</t>
+          <t>2555-43-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36159,12 +36159,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>2639.4</v>
+        <v>8032.96</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1159-41-CM26</t>
+          <t>2146-77-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36224,12 +36224,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -36258,13 +36258,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>32142.72</v>
+        <v>2639.4</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2555-43-CM26</t>
+          <t>1159-41-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36289,12 +36289,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>8032.96</v>
+        <v>32142.72</v>
       </c>
     </row>
     <row r="553">
@@ -37109,7 +37109,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>1432-9-CM26</t>
+          <t>3750-83-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37129,17 +37129,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37168,13 +37168,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>5470.58</v>
+        <v>4376.46</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>3750-83-CM26</t>
+          <t>1432-9-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37194,17 +37194,17 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -37233,13 +37233,13 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>4376.46</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>4433-15-CM26</t>
+          <t>1229788-62-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -37259,17 +37259,17 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -37298,13 +37298,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>2361.21</v>
+        <v>31019.35</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>1229788-62-CM26</t>
+          <t>4433-15-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37324,17 +37324,17 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -37363,7 +37363,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>31019.35</v>
+        <v>2361.21</v>
       </c>
     </row>
     <row r="569">
@@ -37889,7 +37889,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>3707-174-CM26</t>
+          <t>1574-40-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37948,13 +37948,13 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>5454.97</v>
+        <v>6774.85</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1574-40-CM26</t>
+          <t>3707-174-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37979,12 +37979,12 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -38013,7 +38013,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>6774.85</v>
+        <v>5454.97</v>
       </c>
     </row>
     <row r="579">
@@ -38084,7 +38084,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>4247-201-CM26</t>
+          <t>2146-124-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -38104,17 +38104,17 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -38124,12 +38124,12 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
@@ -38143,13 +38143,13 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>32759.68</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2288-293-CM26</t>
+          <t>3754-59-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -38169,7 +38169,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>8735.91</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2146-124-CM26</t>
+          <t>4247-201-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -38234,17 +38234,17 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -38254,12 +38254,12 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K582" t="inlineStr">
@@ -38273,13 +38273,13 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>4367.96</v>
+        <v>32759.68</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2125-665-CM26</t>
+          <t>2288-293-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -38304,12 +38304,12 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -38319,12 +38319,12 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
@@ -38338,13 +38338,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>6551.94</v>
+        <v>8735.91</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>3754-59-CM26</t>
+          <t>2125-665-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -38364,17 +38364,17 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -38384,12 +38384,12 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
@@ -38403,7 +38403,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>10919.89</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="585">
@@ -38604,7 +38604,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>1660-210-CM26</t>
+          <t>3884-169-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -38629,12 +38629,12 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -38663,13 +38663,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>4032.69</v>
+        <v>7721.26</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>3884-169-CM26</t>
+          <t>1660-210-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -38694,12 +38694,12 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -38728,7 +38728,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>7721.26</v>
+        <v>4032.69</v>
       </c>
     </row>
     <row r="590">
@@ -39189,7 +39189,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>4036-191-CM26</t>
+          <t>1276532-10-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -39209,17 +39209,17 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -39248,13 +39248,13 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>20999.02</v>
+        <v>2345.63</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1276532-10-CM26</t>
+          <t>4036-191-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -39274,17 +39274,17 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -39313,7 +39313,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2345.63</v>
+        <v>20999.02</v>
       </c>
     </row>
     <row r="599">
@@ -39384,7 +39384,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>3615-47-CM26</t>
+          <t>3688-173-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -39404,17 +39404,17 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -39443,13 +39443,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>5436.63</v>
+        <v>3914.24</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>3511-106-CM26</t>
+          <t>3615-47-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39469,17 +39469,17 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -39508,13 +39508,13 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>13420.27</v>
+        <v>5436.63</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>3688-173-CM26</t>
+          <t>3511-106-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -39539,12 +39539,12 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -39573,7 +39573,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3914.24</v>
+        <v>13420.27</v>
       </c>
     </row>
     <row r="603">
@@ -39839,7 +39839,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2996-83-CM26</t>
+          <t>3616-46-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39859,17 +39859,17 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -39898,7 +39898,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>4509.74</v>
+        <v>3382.3</v>
       </c>
     </row>
     <row r="608">
@@ -40034,7 +40034,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>3616-46-CM26</t>
+          <t>2996-83-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -40054,17 +40054,17 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -40093,7 +40093,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>3382.3</v>
+        <v>4509.74</v>
       </c>
     </row>
     <row r="611">
@@ -41074,7 +41074,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>1057440-237-CM26</t>
+          <t>4433-24-CM26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -41094,17 +41094,17 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -41133,13 +41133,13 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>3914.2</v>
+        <v>3668.17</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>1159-82-CM26</t>
+          <t>1159-83-CM26</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -41179,17 +41179,17 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L627" t="inlineStr">
@@ -41198,13 +41198,13 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>17334.32</v>
+        <v>10624.26</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>3615-58-CM26</t>
+          <t>3884-213-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -41229,12 +41229,12 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -41263,13 +41263,13 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2454.81</v>
+        <v>8205.84</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>4433-24-CM26</t>
+          <t>1057440-237-CM26</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -41289,17 +41289,17 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -41328,13 +41328,13 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>3668.17</v>
+        <v>3914.2</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1159-83-CM26</t>
+          <t>3615-58-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -41359,12 +41359,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -41374,17 +41374,17 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -41393,13 +41393,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>10624.26</v>
+        <v>2454.81</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>3884-213-CM26</t>
+          <t>1159-82-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41424,12 +41424,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -41458,7 +41458,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>8205.84</v>
+        <v>17334.32</v>
       </c>
     </row>
     <row r="632">
@@ -41919,7 +41919,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>1159-90-CM26</t>
+          <t>1343-95-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -41944,12 +41944,12 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.511.042-8</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -41978,13 +41978,13 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>22400.68</v>
+        <v>2372.23</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>1159-91-CM26</t>
+          <t>1159-90-CM26</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -42024,17 +42024,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -42049,7 +42049,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>1343-95-CM26</t>
+          <t>1159-91-CM26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -42074,12 +42074,12 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>60.511.042-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LIMARÍ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -42089,17 +42089,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -42108,13 +42108,13 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2372.23</v>
+        <v>22400.68</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>1432-14-CM26</t>
+          <t>2711-111-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -42134,17 +42134,17 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -42173,13 +42173,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>5600.17</v>
+        <v>5040.15</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2711-111-CM26</t>
+          <t>1432-14-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42199,17 +42199,17 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -42238,7 +42238,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>5040.15</v>
+        <v>5600.17</v>
       </c>
     </row>
     <row r="644">
@@ -42309,7 +42309,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>1962-253-CM26</t>
+          <t>646-51-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42334,12 +42334,12 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>10701.69</v>
+        <v>22529.88</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>646-51-CM26</t>
+          <t>1962-253-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -42399,12 +42399,12 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -42433,7 +42433,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>22529.88</v>
+        <v>10701.69</v>
       </c>
     </row>
     <row r="647">
@@ -43089,7 +43089,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>1660-366-CM26</t>
+          <t>2288-429-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -43114,12 +43114,12 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -43129,12 +43129,12 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
@@ -43148,7 +43148,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>12483.27</v>
+        <v>16869.29</v>
       </c>
     </row>
     <row r="658">
@@ -43284,7 +43284,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2288-429-CM26</t>
+          <t>1660-366-CM26</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -43324,12 +43324,12 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
@@ -43343,7 +43343,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>16869.29</v>
+        <v>12483.27</v>
       </c>
     </row>
     <row r="661">
@@ -43999,7 +43999,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>5158-58-CM26</t>
+          <t>1346282-232-CM26</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -44019,17 +44019,17 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -44058,13 +44058,13 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>8956.059999999999</v>
+        <v>4813.88</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>1346282-232-CM26</t>
+          <t>5158-58-CM26</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -44084,17 +44084,17 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>4813.88</v>
+        <v>8956.059999999999</v>
       </c>
     </row>
     <row r="673">
@@ -44194,7 +44194,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>1159-111-CM26</t>
+          <t>2711-125-CM26</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -44214,17 +44214,17 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -44253,13 +44253,13 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>31564.26</v>
+        <v>5037.78</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2711-125-CM26</t>
+          <t>1159-111-CM26</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -44279,17 +44279,17 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>5037.78</v>
+        <v>31564.26</v>
       </c>
     </row>
     <row r="676">
@@ -45169,7 +45169,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>3265-271-CM26</t>
+          <t>2450-617-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -45189,17 +45189,17 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -45228,13 +45228,13 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>14915.12</v>
+        <v>38266.1</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2450-617-CM26</t>
+          <t>3265-270-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -45254,17 +45254,17 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -45293,13 +45293,13 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>38266.1</v>
+        <v>23503.98</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>4247-335-CM26</t>
+          <t>3265-271-CM26</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -45324,12 +45324,12 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -45339,12 +45339,12 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
@@ -45358,13 +45358,13 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>11256.7</v>
+        <v>14915.12</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>3265-270-CM26</t>
+          <t>2125-1225-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -45384,17 +45384,17 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -45423,13 +45423,13 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>23503.98</v>
+        <v>6754.02</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2125-1225-CM26</t>
+          <t>4247-335-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -45449,17 +45449,17 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -45469,12 +45469,12 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
@@ -45488,7 +45488,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>6754.02</v>
+        <v>11256.7</v>
       </c>
     </row>
     <row r="694">
@@ -45949,7 +45949,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>697055-31-CM26</t>
+          <t>4773-11-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45974,12 +45974,12 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -45989,17 +45989,17 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L701" t="inlineStr">
@@ -46008,13 +46008,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>5458.69</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>1057440-323-CM26</t>
+          <t>697055-31-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -46039,12 +46039,12 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -46073,13 +46073,13 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>3821.09</v>
+        <v>5458.69</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>4036-278-CM26</t>
+          <t>1057440-323-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -46099,17 +46099,17 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -46138,13 +46138,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>24673.3</v>
+        <v>3821.09</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>1962-333-CM26</t>
+          <t>4036-278-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -46164,17 +46164,17 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -46203,13 +46203,13 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2729.35</v>
+        <v>24673.3</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>4773-11-CM26</t>
+          <t>1962-333-CM26</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -46234,12 +46234,12 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -46249,17 +46249,17 @@
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -46268,7 +46268,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2358.16</v>
+        <v>2729.35</v>
       </c>
     </row>
     <row r="706">
@@ -46339,7 +46339,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2145-527-CM26</t>
+          <t>2711-149-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46359,17 +46359,17 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -46398,13 +46398,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>3850.3</v>
+        <v>5500.43</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2711-149-CM26</t>
+          <t>2145-527-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -46424,17 +46424,17 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -46463,13 +46463,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>5500.43</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>3687-169-CM26</t>
+          <t>3688-281-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46528,13 +46528,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>3932.01</v>
+        <v>4493.73</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>1962-343-CM26</t>
+          <t>3687-169-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46554,17 +46554,17 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -46593,13 +46593,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>8425.74</v>
+        <v>3932.01</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>3707-319-CM26</t>
+          <t>1962-343-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -46624,12 +46624,12 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -46658,13 +46658,13 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>8498.76</v>
+        <v>8425.74</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>3688-281-CM26</t>
+          <t>3707-319-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46684,17 +46684,17 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -46723,7 +46723,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>4493.73</v>
+        <v>8498.76</v>
       </c>
     </row>
     <row r="713">
@@ -47184,7 +47184,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>1276532-15-CM26</t>
+          <t>3512-603-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47204,17 +47204,17 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -47243,13 +47243,13 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>2373.64</v>
+        <v>17664.33</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>3512-603-CM26</t>
+          <t>1276532-15-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47269,17 +47269,17 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -47308,7 +47308,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>17664.33</v>
+        <v>2373.64</v>
       </c>
     </row>
     <row r="722">
@@ -48614,7 +48614,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>931-126-CM26</t>
+          <t>3707-365-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48639,12 +48639,12 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -48673,13 +48673,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>2314.34</v>
+        <v>6684.68</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>4433-48-CM26</t>
+          <t>931-126-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48699,17 +48699,17 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -48738,13 +48738,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>2796.08</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>1242121-353-CM26</t>
+          <t>4433-48-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -48764,17 +48764,17 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -48803,13 +48803,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>6458.63</v>
+        <v>2796.08</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>3707-365-CM26</t>
+          <t>1242121-353-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48834,12 +48834,12 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -48868,13 +48868,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>6684.68</v>
+        <v>6458.63</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>1057439-4664-CM26</t>
+          <t>3512-645-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48894,17 +48894,17 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -48933,13 +48933,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>4648.95</v>
+        <v>17298.42</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>1159-191-CM26</t>
+          <t>1057439-4664-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48964,12 +48964,12 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -48998,13 +48998,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>15892.92</v>
+        <v>4648.95</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>3512-645-CM26</t>
+          <t>1159-191-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -49024,17 +49024,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -49063,7 +49063,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>17298.42</v>
+        <v>15892.92</v>
       </c>
     </row>
     <row r="749">
@@ -49329,7 +49329,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>1057438-181-CM26</t>
+          <t>527481-76-CM26</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -49354,12 +49354,12 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -49388,13 +49388,13 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>7569.37</v>
+        <v>10849.28</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>3873-8503-CM26</t>
+          <t>1057438-181-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -49419,12 +49419,12 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -49434,12 +49434,12 @@
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
@@ -49453,13 +49453,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2703.35</v>
+        <v>7569.37</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>527481-76-CM26</t>
+          <t>3873-8503-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49484,12 +49484,12 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -49499,12 +49499,12 @@
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K755" t="inlineStr">
@@ -49518,13 +49518,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>10849.28</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>3597-469-CM26</t>
+          <t>1159-197-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -49544,17 +49544,17 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -49583,7 +49583,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>21950.49</v>
+        <v>21415.11</v>
       </c>
     </row>
     <row r="757">
@@ -49654,7 +49654,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>1159-197-CM26</t>
+          <t>3597-469-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -49674,17 +49674,17 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -49713,7 +49713,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>21415.11</v>
+        <v>21950.49</v>
       </c>
     </row>
     <row r="759">
@@ -50109,7 +50109,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>3707-391-CM26</t>
+          <t>3707-390-CM26</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -50168,13 +50168,13 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>3962.42</v>
+        <v>6568.8</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>3707-390-CM26</t>
+          <t>3707-391-CM26</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -50233,7 +50233,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>6568.8</v>
+        <v>3962.42</v>
       </c>
     </row>
     <row r="767">
@@ -50369,7 +50369,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>3750-190-CM26</t>
+          <t>1057440-426-CM26</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -50389,17 +50389,17 @@
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
@@ -50428,13 +50428,13 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>4308.39</v>
+        <v>3769.85</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2145-710-CM26</t>
+          <t>3750-190-CM26</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -50454,17 +50454,17 @@
       </c>
       <c r="E770" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -50493,13 +50493,13 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>3769.85</v>
+        <v>4308.39</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>1057440-426-CM26</t>
+          <t>2145-710-CM26</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -50524,12 +50524,12 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -50564,7 +50564,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>3707-400-CM26</t>
+          <t>3688-350-CM26</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -50584,17 +50584,17 @@
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.400-7</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE SALAMANCA</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -50623,13 +50623,13 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>7568.47</v>
+        <v>4324.84</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>3688-350-CM26</t>
+          <t>3707-400-CM26</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -50649,17 +50649,17 @@
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>69.041.400-7</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SALAMANCA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -50688,7 +50688,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>4324.84</v>
+        <v>7568.47</v>
       </c>
     </row>
     <row r="774">
@@ -50824,7 +50824,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>1305532-60-CM26</t>
+          <t>3512-722-CM26</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -50844,17 +50844,17 @@
       </c>
       <c r="E776" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -50883,13 +50883,13 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>3290.99</v>
+        <v>24133.92</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>3512-722-CM26</t>
+          <t>1305532-60-CM26</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -50909,17 +50909,17 @@
       </c>
       <c r="E777" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -50948,7 +50948,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>24133.92</v>
+        <v>3290.99</v>
       </c>
     </row>
     <row r="778">
@@ -51344,7 +51344,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>3712-541-CM26</t>
+          <t>4247-470-CM26</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -51364,17 +51364,17 @@
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -51384,12 +51384,12 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
@@ -51403,7 +51403,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>32894.74</v>
+        <v>2741.23</v>
       </c>
     </row>
     <row r="785">
@@ -51474,7 +51474,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>3884-424-CM26</t>
+          <t>3712-541-CM26</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -51499,12 +51499,12 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -51533,13 +51533,13 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>2895.83</v>
+        <v>32894.74</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>707418-112-CM26</t>
+          <t>3884-424-CM26</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -51564,12 +51564,12 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -51598,13 +51598,13 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>3947.37</v>
+        <v>2895.83</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>4247-470-CM26</t>
+          <t>707418-112-CM26</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -51624,17 +51624,17 @@
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -51644,12 +51644,12 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
@@ -51663,13 +51663,13 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>2741.23</v>
+        <v>3947.37</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>1495203-17-CM26</t>
+          <t>3260-118-CM26</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -51689,17 +51689,17 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -51728,13 +51728,13 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>24489.71</v>
+        <v>4161.19</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>3597-537-CM26</t>
+          <t>1495203-17-CM26</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -51754,17 +51754,17 @@
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -51793,13 +51793,13 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>22448.53</v>
+        <v>24489.71</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>1107276-271-CM26</t>
+          <t>3597-537-CM26</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -51819,17 +51819,17 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -51858,13 +51858,13 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>2409.11</v>
+        <v>22448.53</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>527481-82-CM26</t>
+          <t>1107276-271-CM26</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -51884,17 +51884,17 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -51923,13 +51923,13 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>36136.75</v>
+        <v>2409.11</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>3260-118-CM26</t>
+          <t>527481-82-CM26</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -51954,12 +51954,12 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -51988,7 +51988,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>4161.19</v>
+        <v>36136.75</v>
       </c>
     </row>
     <row r="794">
@@ -53099,7 +53099,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>1057439-5675-CM26</t>
+          <t>3707-457-CM26</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -53124,12 +53124,12 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -53158,13 +53158,13 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>4592.45</v>
+        <v>7476.08</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>3707-457-CM26</t>
+          <t>1057439-5675-CM26</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -53189,12 +53189,12 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -53223,7 +53223,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>7476.08</v>
+        <v>4592.45</v>
       </c>
     </row>
     <row r="813">
@@ -53359,7 +53359,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>1242121-465-CM26</t>
+          <t>1129-47-CM26</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -53384,12 +53384,12 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -53418,13 +53418,13 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>6421.58</v>
+        <v>2302.81</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>1129-47-CM26</t>
+          <t>1242121-465-CM26</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -53449,12 +53449,12 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -53483,13 +53483,13 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>2302.81</v>
+        <v>6421.58</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>931-159-CM26</t>
+          <t>1159-259-CM26</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -53509,17 +53509,17 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H817" t="inlineStr">
@@ -53548,7 +53548,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>2677.18</v>
+        <v>50330.9</v>
       </c>
     </row>
     <row r="818">
@@ -53684,7 +53684,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>1057438-254-CM26</t>
+          <t>931-159-CM26</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -53709,12 +53709,12 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -53743,13 +53743,13 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>4283.48</v>
+        <v>2677.18</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>1159-259-CM26</t>
+          <t>1057438-254-CM26</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -53769,17 +53769,17 @@
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
@@ -53808,7 +53808,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>50330.9</v>
+        <v>4283.48</v>
       </c>
     </row>
     <row r="822">
@@ -54204,7 +54204,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>3707-470-CM26</t>
+          <t>3714-259-CM26</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -54229,12 +54229,12 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -54263,13 +54263,13 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>7298.57</v>
+        <v>7469.3</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>3714-259-CM26</t>
+          <t>3707-470-CM26</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -54294,12 +54294,12 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -54328,7 +54328,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>7469.3</v>
+        <v>7298.57</v>
       </c>
     </row>
     <row r="830">
@@ -54984,7 +54984,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2450-983-CM26</t>
+          <t>2710-623-CM26</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -55009,12 +55009,12 @@
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -55043,13 +55043,13 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>5919.36</v>
+        <v>36870.17</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2710-623-CM26</t>
+          <t>3707-497-CM26</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -55074,12 +55074,12 @@
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H841" t="inlineStr">
@@ -55108,7 +55108,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>36870.17</v>
+        <v>7528.1</v>
       </c>
     </row>
     <row r="842">
@@ -55244,7 +55244,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>3707-497-CM26</t>
+          <t>2450-983-CM26</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -55269,12 +55269,12 @@
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
@@ -55303,7 +55303,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>7528.1</v>
+        <v>5919.36</v>
       </c>
     </row>
     <row r="845">
@@ -56304,7 +56304,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
@@ -56369,7 +56369,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -57019,7 +57019,7 @@
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
@@ -57084,7 +57084,7 @@
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
@@ -57194,65 +57194,130 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
+          <t>2448-1208-CM26</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M874" s="2" t="n">
+        <v>17231.24</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
           <t>4295-93-CM26</t>
         </is>
       </c>
-      <c r="B874" t="inlineStr">
+      <c r="B875" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C874" t="inlineStr">
+      <c r="C875" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr">
+      <c r="D875" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E874" t="inlineStr">
+      <c r="E875" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F874" t="inlineStr">
+      <c r="F875" t="inlineStr">
         <is>
           <t>69.040.100-2</t>
         </is>
       </c>
-      <c r="G874" t="inlineStr">
+      <c r="G875" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
-      <c r="H874" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I874" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J874" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K874" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L874" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M874" s="2" t="n">
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M875" s="2" t="n">
         <v>243264.61</v>
       </c>
     </row>
